--- a/output/pdf_financials_xlsx/NBVA.xlsx
+++ b/output/pdf_financials_xlsx/NBVA.xlsx
@@ -3640,31 +3640,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.008122000000000001</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.259962</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.628841</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.704628</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.306357</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.082851</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>3.137452</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.485555</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.315979</v>
       </c>
     </row>
     <row r="93">
@@ -6199,7 +6199,11 @@
           <t>Reserves 15</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -7650,7 +7654,11 @@
           <t>Reserves (note 14)</t>
         </is>
       </c>
-      <c r="D43" t="inlineStr"/>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
@@ -9024,7 +9032,11 @@
           <t>Share-based payment reserve (note 11)</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr"/>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
         <v>0.008122000000000001</v>
       </c>

--- a/output/pdf_financials_xlsx/NBVA.xlsx
+++ b/output/pdf_financials_xlsx/NBVA.xlsx
@@ -738,28 +738,28 @@
         </is>
       </c>
       <c r="C10" s="3" t="n">
-        <v>1.188693</v>
+        <v>2.441743</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>1.042891</v>
+        <v>3.577085</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>1.635613</v>
+        <v>4.0258</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>1.159629</v>
+        <v>3.251981</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>1.205318</v>
+        <v>3.555217</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>1.265915</v>
+        <v>4.029546</v>
       </c>
       <c r="I10" s="3" t="n">
-        <v>1.293544</v>
+        <v>3.061334</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>0.556705</v>
+        <v>1.444451</v>
       </c>
     </row>
     <row r="11">
@@ -774,28 +774,28 @@
         </is>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.48118</v>
+        <v>-1.73423</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.196513</v>
+        <v>-2.730707</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-1.477903</v>
+        <v>-3.86809</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>0.805006</v>
+        <v>-1.287346</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.969675</v>
+        <v>-3.319574</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>0.805739</v>
+        <v>-1.957892</v>
       </c>
       <c r="I11" s="3" t="n">
-        <v>0.495439</v>
+        <v>-1.272351</v>
       </c>
       <c r="J11" s="3" t="n">
-        <v>-0.026089</v>
+        <v>-0.913835</v>
       </c>
     </row>
     <row r="12">
@@ -810,10 +810,10 @@
         </is>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.009438999999999999</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.051691</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1428,10 +1428,10 @@
         </is>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-4.929299</v>
+        <v>-4.938738</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-3.532779</v>
+        <v>-3.58447</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-3.783511</v>
@@ -1500,10 +1500,10 @@
         </is>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-4.929299</v>
+        <v>-4.938738</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-3.532779</v>
+        <v>-3.58447</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-3.783511</v>
@@ -1536,10 +1536,10 @@
         </is>
       </c>
       <c r="C30" s="3" t="n">
-        <v>-696.7079050137595</v>
+        <v>-698.0420147757003</v>
       </c>
       <c r="D30" s="3" t="n">
-        <v>-417.3996724867612</v>
+        <v>-423.5069909662113</v>
       </c>
       <c r="E30" s="3" t="n">
         <v>-2399.030499017184</v>
@@ -1646,10 +1646,10 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.915135</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>7.501346</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>0</v>
@@ -1714,10 +1714,10 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.915135</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>7.501346</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>0</v>
@@ -2122,10 +2122,10 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.929686</v>
+        <v>0.014551</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>7.722554</v>
+        <v>0.221208</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>5.443268</v>
@@ -8400,7 +8400,7 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E55" s="5" t="n">
@@ -14615,7 +14615,7 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -16360,7 +16360,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -17816,7 +17816,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -19480,7 +19480,7 @@
       </c>
       <c r="D241" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E241" t="inlineStr">

--- a/output/pdf_financials_xlsx/NBVA.xlsx
+++ b/output/pdf_financials_xlsx/NBVA.xlsx
@@ -552,10 +552,8 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C5" s="3" t="n">
         <v>0</v>
@@ -624,10 +622,8 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C7" s="3" t="n">
         <v>0</v>
@@ -660,10 +656,8 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0.658814</v>
       </c>
       <c r="C8" s="3" t="n">
         <v>1.188693</v>
@@ -696,10 +690,8 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C9" s="3" t="n">
         <v>0</v>
@@ -732,10 +724,8 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.73687</v>
       </c>
       <c r="C10" s="3" t="n">
         <v>2.441743</v>
@@ -804,10 +794,8 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
         <v>0.009438999999999999</v>
@@ -840,10 +828,8 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
         <v>-0</v>
@@ -876,10 +862,8 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C14" s="3" t="n">
         <v>0</v>
@@ -912,10 +896,8 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>0.001562</v>
       </c>
       <c r="C15" s="3" t="n">
         <v>-0.09519</v>
@@ -948,10 +930,8 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.738432</v>
       </c>
       <c r="C16" s="3" t="n">
         <v>-4.929299</v>
@@ -984,10 +964,8 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
         <v>-0</v>
@@ -1011,7 +989,7 @@
         <v>0.1533</v>
       </c>
       <c r="J17" s="3" t="n">
-        <v>0.004271</v>
+        <v>-0.004271</v>
       </c>
     </row>
     <row r="18">
@@ -1124,16 +1102,14 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.738432</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>-4.929299</v>
+        <v>-4.401452</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>-3.532779</v>
+        <v>-4.057961</v>
       </c>
       <c r="E20" s="3" t="n">
         <v>-3.783511</v>
@@ -1160,16 +1136,14 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C21" s="3" t="n">
-        <v>0</v>
+        <v>-0.527847</v>
       </c>
       <c r="D21" s="3" t="n">
-        <v>0</v>
+        <v>-0.356619</v>
       </c>
       <c r="E21" s="3" t="n">
         <v>0</v>
@@ -1196,10 +1170,8 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C22" s="3" t="n">
         <v>0</v>
@@ -1266,15 +1238,11 @@
           <t>EPS (Basic)</t>
         </is>
       </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B24" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="C24" s="3" t="n">
+        <v>-0.1</v>
       </c>
       <c r="D24" s="1" t="inlineStr">
         <is>
@@ -1318,15 +1286,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.02</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.1</v>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
@@ -1370,15 +1334,11 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>36.9216</v>
+      </c>
+      <c r="C26" s="3" t="n">
+        <v>49.29299</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1422,10 +1382,8 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.738432</v>
       </c>
       <c r="C27" s="3" t="n">
         <v>-4.938738</v>
@@ -1458,10 +1416,8 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C28" s="3" t="n">
         <v>0</v>
@@ -1494,10 +1450,8 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.738432</v>
       </c>
       <c r="C29" s="3" t="n">
         <v>-4.938738</v>
@@ -1566,10 +1520,8 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
         <v>-0</v>
@@ -2789,28 +2741,28 @@
         <v>0</v>
       </c>
       <c r="C67" s="3" t="n">
-        <v>0</v>
+        <v>0.256304</v>
       </c>
       <c r="D67" s="3" t="n">
-        <v>0</v>
+        <v>0.336188</v>
       </c>
       <c r="E67" s="3" t="n">
-        <v>0</v>
+        <v>0.49486</v>
       </c>
       <c r="F67" s="3" t="n">
-        <v>0</v>
+        <v>0.116889</v>
       </c>
       <c r="G67" s="3" t="n">
-        <v>0</v>
+        <v>0.099998</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>0.108376</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.08493000000000001</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.087544</v>
       </c>
     </row>
     <row r="68">
@@ -5207,7 +5159,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M299"/>
+  <dimension ref="A1:M325"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -14618,10 +14570,8 @@
           <t>OperatingExpense</t>
         </is>
       </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E160" s="5" t="n">
+        <v>0.73687</v>
       </c>
       <c r="F160" s="5" t="n">
         <v>2.441743</v>
@@ -15140,7 +15090,11 @@
           <t>Income tax recovery (expense) 16</t>
         </is>
       </c>
-      <c r="D169" t="inlineStr"/>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E169" t="inlineStr">
         <is>
           <t>-</t>
@@ -16426,15 +16380,11 @@
           <t>OtherIncomeExpense</t>
         </is>
       </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E190" s="5" t="n">
+        <v>0.001562</v>
+      </c>
+      <c r="F190" s="5" t="n">
+        <v>-0.09519</v>
       </c>
       <c r="G190" t="inlineStr">
         <is>
@@ -22140,7 +22090,11 @@
           <t>Net Loss from continuing operations</t>
         </is>
       </c>
-      <c r="D285" t="inlineStr"/>
+      <c r="D285" t="inlineStr">
+        <is>
+          <t>NetIncomeContinuousOperations</t>
+        </is>
+      </c>
       <c r="E285" t="inlineStr">
         <is>
           <t>-</t>
@@ -22265,10 +22219,8 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E287" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E287" s="5" t="n">
+        <v>-0.738432</v>
       </c>
       <c r="F287" s="5" t="n">
         <v>-4.929299</v>
@@ -23034,6 +22986,1596 @@
         </is>
       </c>
       <c r="M299" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>(formerly Sherpa Holdings Corp.)</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>Revenue (note 14) $</t>
+        </is>
+      </c>
+      <c r="D300" t="inlineStr">
+        <is>
+          <t>TotalRevenue</t>
+        </is>
+      </c>
+      <c r="E300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F300" s="5" t="n">
+        <v>0.7075129999999999</v>
+      </c>
+      <c r="G300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>General and administrative (note 13)</t>
+        </is>
+      </c>
+      <c r="D301" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E301" s="5" t="n">
+        <v>0.068454</v>
+      </c>
+      <c r="F301" s="5" t="n">
+        <v>0.430977</v>
+      </c>
+      <c r="G301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M301" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>Research and development (note 13)</t>
+        </is>
+      </c>
+      <c r="D302" t="inlineStr">
+        <is>
+          <t>ResearchAndDevelopment</t>
+        </is>
+      </c>
+      <c r="E302" s="5" t="n">
+        <v>0.658814</v>
+      </c>
+      <c r="F302" s="5" t="n">
+        <v>1.71654</v>
+      </c>
+      <c r="G302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M302" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>Sales and marketing (note 13)</t>
+        </is>
+      </c>
+      <c r="D303" t="inlineStr">
+        <is>
+          <t>SellingAndMarketingExpense</t>
+        </is>
+      </c>
+      <c r="E303" s="5" t="n">
+        <v>0.00148</v>
+      </c>
+      <c r="F303" s="5" t="n">
+        <v>0.590759</v>
+      </c>
+      <c r="G303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M303" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>Share-based compensation (note 11)</t>
+        </is>
+      </c>
+      <c r="D304" t="inlineStr"/>
+      <c r="E304" s="5" t="n">
+        <v>0.008122000000000001</v>
+      </c>
+      <c r="F304" s="5" t="n">
+        <v>0.231314</v>
+      </c>
+      <c r="G304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M304" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>Listing expense (note 10)</t>
+        </is>
+      </c>
+      <c r="D305" t="inlineStr"/>
+      <c r="E305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F305" s="5" t="n">
+        <v>-1.130319</v>
+      </c>
+      <c r="G305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M305" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>Other Items</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>Fair value loss on debt (note 11)</t>
+        </is>
+      </c>
+      <c r="D306" t="inlineStr"/>
+      <c r="E306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F306" s="5" t="n">
+        <v>-1.451152</v>
+      </c>
+      <c r="G306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M306" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>Foreign currency translation adjustment</t>
+        </is>
+      </c>
+      <c r="D307" t="inlineStr"/>
+      <c r="E307" s="5" t="n">
+        <v>-0.001036</v>
+      </c>
+      <c r="F307" s="5" t="n">
+        <v>-0.037436</v>
+      </c>
+      <c r="G307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M307" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>Total Comprehensive Loss $</t>
+        </is>
+      </c>
+      <c r="D308" t="inlineStr"/>
+      <c r="E308" s="5" t="n">
+        <v>-0.739468</v>
+      </c>
+      <c r="F308" s="5" t="n">
+        <v>-4.966735</v>
+      </c>
+      <c r="G308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M308" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D309" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E309" s="5" t="n">
+        <v>-2e-08</v>
+      </c>
+      <c r="F309" s="5" t="n">
+        <v>-1e-07</v>
+      </c>
+      <c r="G309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M309" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>Weighted average number of common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D310" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
+      <c r="E310" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="F310" s="5" t="n">
+        <v>47.949167</v>
+      </c>
+      <c r="G310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M310" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>Balance April 30, 2016 40,000,000 $ 4,000 $ - $ - $ (3,286) $</t>
+        </is>
+      </c>
+      <c r="D311" t="inlineStr"/>
+      <c r="E311" s="5" t="n">
+        <v>0.000714</v>
+      </c>
+      <c r="F311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M311" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>Share- based compensation (note 11) - - 8,122 - -</t>
+        </is>
+      </c>
+      <c r="D312" t="inlineStr"/>
+      <c r="E312" s="5" t="n">
+        <v>0.008122000000000001</v>
+      </c>
+      <c r="F312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M312" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>Other comprehensive loss - - - - -</t>
+        </is>
+      </c>
+      <c r="D313" t="inlineStr"/>
+      <c r="E313" s="5" t="n">
+        <v>-0.001036</v>
+      </c>
+      <c r="F313" s="5" t="n">
+        <v>-0.001036</v>
+      </c>
+      <c r="G313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M313" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - - (738,432)</t>
+        </is>
+      </c>
+      <c r="D314" t="inlineStr"/>
+      <c r="E314" s="5" t="n">
+        <v>-0.738432</v>
+      </c>
+      <c r="F314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M314" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>Balance April 30, 2017 40,000,000 4,000 8,122 - (741,718)</t>
+        </is>
+      </c>
+      <c r="D315" t="inlineStr"/>
+      <c r="E315" s="5" t="n">
+        <v>-0.7306319999999999</v>
+      </c>
+      <c r="F315" s="5" t="n">
+        <v>-0.001036</v>
+      </c>
+      <c r="G315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M315" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>Share- based compensation (note 11) - - 143,345 87,969 -</t>
+        </is>
+      </c>
+      <c r="D316" t="inlineStr"/>
+      <c r="E316" s="5" t="n">
+        <v>0.231314</v>
+      </c>
+      <c r="F316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M316" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>Reduction of shares due to reverse acquisition (note 10) (9,032,257) - - - -</t>
+        </is>
+      </c>
+      <c r="D317" t="inlineStr"/>
+      <c r="E317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M317" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>Options exercised (note 11) 286,452 136,263 (59,101) - -</t>
+        </is>
+      </c>
+      <c r="D318" t="inlineStr"/>
+      <c r="E318" s="5" t="n">
+        <v>0.07716199999999999</v>
+      </c>
+      <c r="F318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M318" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>Issued for cash, net (note 11) 19,355 12,000 - - -</t>
+        </is>
+      </c>
+      <c r="D319" t="inlineStr"/>
+      <c r="E319" s="5" t="n">
+        <v>0.012</v>
+      </c>
+      <c r="F319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M319" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>Issued for cash, net (notes 10 and 11) 13,032,284 7,007,840 - 272,512 -</t>
+        </is>
+      </c>
+      <c r="D320" t="inlineStr"/>
+      <c r="E320" s="5" t="n">
+        <v>7.280352</v>
+      </c>
+      <c r="F320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M320" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>Warrants exercised (note 11) 804,357 755,194 - (283,381) -</t>
+        </is>
+      </c>
+      <c r="D321" t="inlineStr"/>
+      <c r="E321" s="5" t="n">
+        <v>0.471813</v>
+      </c>
+      <c r="F321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M321" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>Issued on conversion of SAFE Agreements (note 11) 6,117,607 3,701,152 - - -</t>
+        </is>
+      </c>
+      <c r="D322" t="inlineStr"/>
+      <c r="E322" s="5" t="n">
+        <v>3.701152</v>
+      </c>
+      <c r="F322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M322" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>Reverse acquisition (note 10) 1,551,100 938,483 63,457 27,039 -</t>
+        </is>
+      </c>
+      <c r="D323" t="inlineStr"/>
+      <c r="E323" s="5" t="n">
+        <v>1.028979</v>
+      </c>
+      <c r="F323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M323" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>Net loss for the year - - - - (4,929,299)</t>
+        </is>
+      </c>
+      <c r="D324" t="inlineStr"/>
+      <c r="E324" s="5" t="n">
+        <v>-4.929299</v>
+      </c>
+      <c r="F324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M324" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Shares         Amount           Options        Warrants                Deficit               Loss                  Total</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>Balance April 30, 2018 52,778,898 $ 12,554,932 $ 155,823 $ 104,139 $ (5,671,017) $</t>
+        </is>
+      </c>
+      <c r="D325" t="inlineStr"/>
+      <c r="E325" s="5" t="n">
+        <v>7.105405</v>
+      </c>
+      <c r="F325" s="5" t="n">
+        <v>-0.038472</v>
+      </c>
+      <c r="G325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L325" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M325" t="inlineStr">
         <is>
           <t>-</t>
         </is>
